--- a/docs/视频评分榜.xlsx
+++ b/docs/视频评分榜.xlsx
@@ -10662,7 +10662,7 @@
       <c r="J3" s="5" t="n"/>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
@@ -10696,7 +10696,7 @@
       <c r="V3" s="5" t="n"/>
       <c r="W3" s="6" t="inlineStr">
         <is>
-          <t>S+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="X3" s="7" t="inlineStr">
@@ -11135,7 +11135,7 @@
       <c r="J11" s="5" t="n"/>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -11400,7 +11400,7 @@
       <c r="P15" s="5" t="n"/>
       <c r="Q15" s="14" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="R15" s="7" t="inlineStr">
@@ -11434,7 +11434,7 @@
       <c r="AB15" s="5" t="n"/>
       <c r="AC15" s="14" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AD15" s="7" t="inlineStr">
@@ -11670,7 +11670,7 @@
       <c r="V19" s="5" t="n"/>
       <c r="W19" s="16" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X19" s="7" t="inlineStr">
@@ -11687,7 +11687,7 @@
       <c r="AB19" s="5" t="n"/>
       <c r="AC19" s="16" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AD19" s="7" t="inlineStr">
@@ -12154,7 +12154,7 @@
       <c r="P27" s="5" t="n"/>
       <c r="Q27" s="18" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="R27" s="7" t="inlineStr">
@@ -12317,7 +12317,7 @@
       <c r="D31" s="5" t="n"/>
       <c r="E31" s="23" t="inlineStr">
         <is>
-          <t>D+</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -12475,7 +12475,7 @@
       <c r="J35" s="5" t="n"/>
       <c r="K35" s="21" t="inlineStr">
         <is>
-          <t>F+</t>
+          <t>F</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
@@ -12509,7 +12509,7 @@
       <c r="V35" s="5" t="n"/>
       <c r="W35" s="21" t="inlineStr">
         <is>
-          <t>F+</t>
+          <t>F</t>
         </is>
       </c>
       <c r="X35" s="7" t="inlineStr">
